--- a/demo 4 (alpha interpolated)/Pb210_results/CA modeling data/elogpb210_md_CA_summary.xlsx
+++ b/demo 4 (alpha interpolated)/Pb210_results/CA modeling data/elogpb210_md_CA_summary.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.667849542065013</v>
+        <v>2.670076419228832</v>
       </c>
       <c r="D2">
-        <v>0.06768004467031864</v>
+        <v>0.06863357038593076</v>
       </c>
       <c r="E2">
-        <v>39.4185546871397</v>
+        <v>38.90335886964395</v>
       </c>
       <c r="F2">
-        <v>2.457289052123273E-29</v>
+        <v>3.759639955975893E-29</v>
       </c>
       <c r="G2">
-        <v>0.9421955702052517</v>
+        <v>0.9412674615592854</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.2755909944161267</v>
+        <v>-0.2771244330301524</v>
       </c>
       <c r="D3">
-        <v>0.01169618207027453</v>
+        <v>0.01186096639381944</v>
       </c>
       <c r="E3">
-        <v>-23.56247472553736</v>
+        <v>-23.36440588640041</v>
       </c>
       <c r="F3">
-        <v>3.233204869773242E-22</v>
+        <v>4.206969147964587E-22</v>
       </c>
       <c r="G3">
-        <v>0.9421955702052517</v>
+        <v>0.9412674615592854</v>
       </c>
     </row>
   </sheetData>
